--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145936</v>
       </c>
       <c r="B3" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145949</v>
       </c>
       <c r="B4" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145968</v>
       </c>
       <c r="B5" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145940</v>
       </c>
       <c r="B6" t="n">
-        <v>79569</v>
+        <v>79571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145952</v>
       </c>
       <c r="B7" t="n">
-        <v>79569</v>
+        <v>79571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145960</v>
       </c>
       <c r="B8" t="n">
-        <v>79569</v>
+        <v>79571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145969</v>
       </c>
       <c r="B9" t="n">
-        <v>79569</v>
+        <v>79571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136145944</v>
       </c>
       <c r="B10" t="n">
-        <v>81456</v>
+        <v>81458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136145971</v>
       </c>
       <c r="B11" t="n">
-        <v>81456</v>
+        <v>81458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136145946</v>
       </c>
       <c r="B16" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136145970</v>
       </c>
       <c r="B17" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136145931</v>
       </c>
       <c r="B18" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145955</v>
       </c>
       <c r="B19" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145967</v>
       </c>
       <c r="B20" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145945</v>
       </c>
       <c r="B21" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145966</v>
       </c>
       <c r="B22" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145941</v>
       </c>
       <c r="B23" t="n">
-        <v>79560</v>
+        <v>79562</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145928</v>
       </c>
       <c r="B24" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145932</v>
       </c>
       <c r="B25" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145938</v>
       </c>
       <c r="B26" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145942</v>
       </c>
       <c r="B27" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145948</v>
       </c>
       <c r="B28" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145956</v>
       </c>
       <c r="B29" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145962</v>
       </c>
       <c r="B30" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145963</v>
       </c>
       <c r="B31" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145930</v>
       </c>
       <c r="B32" t="n">
-        <v>78478</v>
+        <v>78480</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145947</v>
       </c>
       <c r="B33" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>136145935</v>
       </c>
       <c r="B34" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>136145964</v>
       </c>
       <c r="B35" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136145965</v>
       </c>
       <c r="B36" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136145929</v>
       </c>
       <c r="B37" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>136145933</v>
       </c>
       <c r="B38" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>136145951</v>
       </c>
       <c r="B39" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136145953</v>
       </c>
       <c r="B40" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136145959</v>
       </c>
       <c r="B41" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136145954</v>
       </c>
       <c r="B42" t="n">
-        <v>78887</v>
+        <v>78889</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
